--- a/EtatFiFolder/LivreCompta.xlsx
+++ b/EtatFiFolder/LivreCompta.xlsx
@@ -1,36 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="390" yWindow="165" windowWidth="9975" windowHeight="10635" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GrandLivre" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Journal" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,42 +42,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -447,127 +413,49 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>Compte</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>Débit</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>Crédit</t>
-        </is>
-      </c>
-      <c r="D1" s="2" t="inlineStr">
-        <is>
-          <t>Solde</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>53</v>
-      </c>
-      <c r="B2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>108</v>
-      </c>
-      <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-10000000</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>401</v>
-      </c>
-      <c r="B4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>411</v>
-      </c>
-      <c r="B5" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="C5" t="n">
-        <v>3000000</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>512</v>
-      </c>
-      <c r="B6" t="n">
-        <v>20000000</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="D6" t="n">
-        <v>18000000</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>601</v>
-      </c>
-      <c r="B7" t="n">
-        <v>2000000</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>2000000</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>701</v>
-      </c>
-      <c r="B8" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" t="n">
-        <v>10000000</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-10000000</v>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Libellé</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>DateValeur</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>MontantDébit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>MontantCrédit</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>CompteDébit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>CompteCrédit</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Année</t>
+        </is>
       </c>
     </row>
   </sheetData>
